--- a/tool/Population/table/PoblacionDANE_25899RAS.xlsx
+++ b/tool/Population/table/PoblacionDANE_25899RAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\Population\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CE8210-4206-4D51-B7F8-69FD3A1E3F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CC5E8D-D682-4EFF-81D2-6C49C1116A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" tabRatio="769" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="82">
   <si>
     <t>Logarítmica</t>
   </si>
@@ -617,9 +617,6 @@
   </si>
   <si>
     <t>Proyección DANE</t>
-  </si>
-  <si>
-    <t>Población censal y proyectada a 30 años con diferentes tendencias. Municipio de San Luis de Gaceno</t>
   </si>
 </sst>
 </file>
@@ -1462,9 +1459,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1473,6 +1467,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3869,7 +3866,6 @@
         <c:axId val="663400352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="1970"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -8144,7 +8140,7 @@
         <v>3.4411076834780119E-2</v>
       </c>
       <c r="R4" s="61">
-        <f>+(Censal!$D$6/Censal!D2)^(1/(Censal!$C$6-Censal!C2))-1</f>
+        <f>(Censal!$D$6/Censal!D2)^(1/(Censal!$C$6-Censal!C2))-1</f>
         <v>2.5139821342668789E-2</v>
       </c>
       <c r="S4" s="59">
@@ -9443,7 +9439,7 @@
         <v>1410864</v>
       </c>
       <c r="H29" s="56">
-        <f t="shared" si="4"/>
+        <f>ROUND($H$4*$D29^4+$H$5*$D29^3+$H$6*$D29^2+$H$7*$D29+$H$8,0)</f>
         <v>1438378</v>
       </c>
       <c r="I29" s="56">
@@ -9642,9 +9638,6 @@
       <c r="D36" s="9"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B37" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="D37" s="9"/>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
@@ -9782,13 +9775,13 @@
       <c r="F11" s="95"/>
     </row>
     <row r="12" spans="2:7" ht="24" x14ac:dyDescent="0.45">
-      <c r="C12" s="84">
+      <c r="C12" s="83">
         <f>C9+F9</f>
         <v>4</v>
       </c>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="86"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="85"/>
     </row>
     <row r="13" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="C13" s="38" t="s">
@@ -9832,91 +9825,91 @@
       <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
       <c r="G17" s="64">
         <f>(C12/F14)*1000</f>
         <v>3.0851342804695574E-2</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
       <c r="G18" s="64">
         <f>(C4/F14)*1000</f>
         <v>0.13111820691995618</v>
       </c>
     </row>
     <row r="19" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
       <c r="G19" s="64">
         <f>(C7/F14)*1000</f>
         <v>0.13883104262113008</v>
       </c>
     </row>
     <row r="20" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
       <c r="G20" s="64">
         <f>G18-G19</f>
         <v>-7.7128357011738979E-3</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B21" s="83" t="s">
+      <c r="B21" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="86"/>
       <c r="G21" s="64">
         <f>(F4/F14)*1000</f>
         <v>0.23138507103521683</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
       <c r="G22" s="64">
         <f>(F7/F14)*1000</f>
         <v>0.19282089252934734</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="86"/>
       <c r="G23" s="64">
         <f>G21-G22</f>
         <v>3.856417850586949E-2</v>
@@ -9924,6 +9917,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
@@ -9931,11 +9929,6 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/Population/table/PoblacionDANE_25899RAS.xlsx
+++ b/tool/Population/table/PoblacionDANE_25899RAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\Population\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CC5E8D-D682-4EFF-81D2-6C49C1116A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF16F1C-EF7D-46BA-B0FC-6DD397EC946D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6368" windowWidth="28996" windowHeight="15675" tabRatio="769" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" tabRatio="769" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Censal" sheetId="2" r:id="rId1"/>
@@ -1459,6 +1459,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1467,9 +1470,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7061,6 +7061,99 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>902802</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>86966</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>103530</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>45651</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3D88B82-2F03-16C0-815C-853516C2CC2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17513574" y="298173"/>
+          <a:ext cx="5768837" cy="3325565"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>111812</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>207065</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>447260</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>160010</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA051C86-FF7C-2DE0-BC98-6846F9F037EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17670942" y="4207565"/>
+          <a:ext cx="5955199" cy="3116902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
     <xdr:ext cx="12225130" cy="6282359"/>
@@ -7092,7 +7185,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
@@ -7125,7 +7218,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
@@ -8772,7 +8865,7 @@
         <v>186846</v>
       </c>
       <c r="H20" s="16">
-        <f t="shared" ref="H20:H29" si="4">ROUND($H$4*$D20^4+$H$5*$D20^3+$H$6*$D20^2+$H$7*$D20+$H$8,0)</f>
+        <f t="shared" ref="H20:H28" si="4">ROUND($H$4*$D20^4+$H$5*$D20^3+$H$6*$D20^2+$H$7*$D20+$H$8,0)</f>
         <v>187464</v>
       </c>
       <c r="I20" s="16">
@@ -9649,6 +9742,7 @@
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9775,13 +9869,13 @@
       <c r="F11" s="95"/>
     </row>
     <row r="12" spans="2:7" ht="24" x14ac:dyDescent="0.45">
-      <c r="C12" s="83">
+      <c r="C12" s="84">
         <f>C9+F9</f>
         <v>4</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="86"/>
     </row>
     <row r="13" spans="2:7" ht="20.25" x14ac:dyDescent="0.45">
       <c r="C13" s="38" t="s">
@@ -9825,91 +9919,91 @@
       <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
       <c r="G17" s="64">
         <f>(C12/F14)*1000</f>
         <v>3.0851342804695574E-2</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="83" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
       <c r="G18" s="64">
         <f>(C4/F14)*1000</f>
         <v>0.13111820691995618</v>
       </c>
     </row>
     <row r="19" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
       <c r="G19" s="64">
         <f>(C7/F14)*1000</f>
         <v>0.13883104262113008</v>
       </c>
     </row>
     <row r="20" spans="2:7" s="43" customFormat="1" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
       <c r="G20" s="64">
         <f>G18-G19</f>
         <v>-7.7128357011738979E-3</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="86"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
       <c r="G21" s="64">
         <f>(F4/F14)*1000</f>
         <v>0.23138507103521683</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
       <c r="G22" s="64">
         <f>(F7/F14)*1000</f>
         <v>0.19282089252934734</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B23" s="86" t="s">
+      <c r="B23" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="86"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
       <c r="G23" s="64">
         <f>G21-G22</f>
         <v>3.856417850586949E-2</v>
@@ -9917,11 +10011,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
@@ -9929,6 +10018,11 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C11:F11"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
